--- a/app_githuburl.xlsx
+++ b/app_githuburl.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,23 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hadoop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://github.com/apache/hadoop</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>java</t>
         </is>
